--- a/Results3.xlsx
+++ b/Results3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raouf\Desktop\Clan_Chest\Chest_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A2A97C-9DFD-46CB-B40F-E516FE736020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7953AEF4-E842-47BB-B49D-C84F288744CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="-2490" windowWidth="25440" windowHeight="15270" xr2:uid="{F99CF3AC-B132-4419-963E-720F575C39BA}"/>
   </bookViews>
@@ -902,7 +902,9 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
